--- a/arima/arima_results.xlsx
+++ b/arima/arima_results.xlsx
@@ -482,62 +482,62 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>weights</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>best_model</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TestSetRMSE</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TestSetR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TestSetMAE</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TestSetMAPE</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>InSampleRMSE</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>InSampleR2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>InSampleMAE</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>InSampleMAPE</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>ValidationMetricValue</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>models</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>weights</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>best_model</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>InSampleRMSE</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>InSampleMAPE</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>InSampleMAE</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>InSampleR2</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>TestSetRMSE</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>TestSetMAPE</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>TestSetMAE</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>TestSetR2</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,11 @@
           <t>arima</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>{'order': (1, 1, 1), 'seasonal_order': (2, 1, 1, 12)}</t>
@@ -573,34 +577,34 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="b">
+      <c r="L2" t="b">
         <v>1</v>
       </c>
+      <c r="M2" t="n">
+        <v>19.03394747466226</v>
+      </c>
       <c r="N2" t="n">
-        <v>15.24780157265418</v>
+        <v>0.9412600617205399</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04444760936174208</v>
+        <v>15.7418818073057</v>
       </c>
       <c r="P2" t="n">
-        <v>9.610640707862769</v>
+        <v>0.03716989909762373</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9837324456596792</v>
+        <v>15.24560823968999</v>
       </c>
       <c r="R2" t="n">
-        <v>19.03217876678499</v>
+        <v>0.9837371253634108</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03716954135597717</v>
+        <v>9.607128476458948</v>
       </c>
       <c r="T2" t="n">
-        <v>15.74075438729331</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.9412709778969743</v>
-      </c>
+        <v>0.0444441707251009</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,7 +617,11 @@
           <t>arima</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>{'order': (0, 1, 1), 'seasonal_order': (0, 1, 0, 12)}</t>
@@ -636,37 +644,37 @@
           <t>rmse</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>38.03659007857039</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="b">
+      <c r="L3" t="b">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>23.64241698907848</v>
+      </c>
       <c r="N3" t="n">
-        <v>15.70860022221939</v>
+        <v>0.9093726046324578</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04652862562369697</v>
+        <v>19.18714134891898</v>
       </c>
       <c r="P3" t="n">
-        <v>10.26890080272217</v>
+        <v>0.04405412600940016</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9827343561858393</v>
+        <v>15.70860022223594</v>
       </c>
       <c r="R3" t="n">
-        <v>23.64241697268991</v>
+        <v>0.9827343561858028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04405412604545777</v>
+        <v>10.26890080256808</v>
       </c>
       <c r="T3" t="n">
-        <v>19.187141354138</v>
+        <v>0.04652862562286594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9093726047581009</v>
+        <v>38.03659000167248</v>
       </c>
     </row>
     <row r="4">
@@ -680,7 +688,11 @@
           <t>arima</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>{'order': (2, 1, 1), 'seasonal_order': (0, 1, 0, 12), 'trend': None}</t>
@@ -701,34 +713,34 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="b">
+      <c r="L4" t="b">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>23.47560266719421</v>
+      </c>
       <c r="N4" t="n">
-        <v>15.49327287240425</v>
+        <v>0.9106469763256628</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04508090035456818</v>
+        <v>19.63662577864172</v>
       </c>
       <c r="P4" t="n">
-        <v>9.87980248980066</v>
+        <v>0.04593616852649137</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.983204453385641</v>
+        <v>15.49327257977791</v>
       </c>
       <c r="R4" t="n">
-        <v>23.47560286796251</v>
+        <v>0.9832044540200866</v>
       </c>
       <c r="S4" t="n">
-        <v>0.045936171429589</v>
+        <v>9.879795431425485</v>
       </c>
       <c r="T4" t="n">
-        <v>19.63662674554096</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.9106469747973311</v>
-      </c>
+        <v>0.04508087909552163</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -741,7 +753,11 @@
           <t>arima</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>{}</t>
@@ -762,34 +778,34 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="b">
+      <c r="L5" t="b">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>210.9325523595288</v>
+      </c>
       <c r="N5" t="n">
-        <v>119.5490415327716</v>
+        <v>-6.213781245989198</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4424570935150651</v>
+        <v>195.7672785712441</v>
       </c>
       <c r="P5" t="n">
-        <v>100.4429006025519</v>
+        <v>0.4300655889889705</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.442490654175344e-15</v>
+        <v>119.5490415327715</v>
       </c>
       <c r="R5" t="n">
-        <v>210.9325514214316</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4300655866107976</v>
+        <v>100.4429009810966</v>
       </c>
       <c r="T5" t="n">
-        <v>195.7672775604763</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-6.213781181824347</v>
-      </c>
+        <v>0.442457100243436</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -837,16 +853,16 @@
         <v>22282</v>
       </c>
       <c r="B2" t="n">
-        <v>451.0432711763795</v>
+        <v>451.0319052622714</v>
       </c>
       <c r="C2" t="n">
-        <v>446.7583684181605</v>
+        <v>446.7583684023541</v>
       </c>
       <c r="D2" t="n">
-        <v>445.6352216234276</v>
+        <v>445.6353326184507</v>
       </c>
       <c r="E2" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="3">
@@ -854,16 +870,16 @@
         <v>22313</v>
       </c>
       <c r="B3" t="n">
-        <v>424.5466285548688</v>
+        <v>424.511500094353</v>
       </c>
       <c r="C3" t="n">
-        <v>420.7583684181605</v>
+        <v>420.7583684023541</v>
       </c>
       <c r="D3" t="n">
-        <v>420.3954837727698</v>
+        <v>420.395666188466</v>
       </c>
       <c r="E3" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="4">
@@ -871,16 +887,16 @@
         <v>22341</v>
       </c>
       <c r="B4" t="n">
-        <v>466.5785513294697</v>
+        <v>466.5900893239804</v>
       </c>
       <c r="C4" t="n">
-        <v>448.7583684181606</v>
+        <v>448.758368402354</v>
       </c>
       <c r="D4" t="n">
-        <v>449.1989609484064</v>
+        <v>449.1991969966577</v>
       </c>
       <c r="E4" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="5">
@@ -888,16 +904,16 @@
         <v>22372</v>
       </c>
       <c r="B5" t="n">
-        <v>494.6240303202082</v>
+        <v>494.6161563675374</v>
       </c>
       <c r="C5" t="n">
-        <v>490.7583684181606</v>
+        <v>490.7583684023541</v>
       </c>
       <c r="D5" t="n">
-        <v>491.840711143626</v>
+        <v>491.8409880103971</v>
       </c>
       <c r="E5" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="6">
@@ -905,16 +921,16 @@
         <v>22402</v>
       </c>
       <c r="B6" t="n">
-        <v>512.0948713158813</v>
+        <v>512.1121703047836</v>
       </c>
       <c r="C6" t="n">
-        <v>501.7583684181606</v>
+        <v>501.7583684023541</v>
       </c>
       <c r="D6" t="n">
-        <v>503.3953374086595</v>
+        <v>503.3956435265699</v>
       </c>
       <c r="E6" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="7">
@@ -922,16 +938,16 @@
         <v>22433</v>
       </c>
       <c r="B7" t="n">
-        <v>575.6218883237901</v>
+        <v>575.669045577658</v>
       </c>
       <c r="C7" t="n">
-        <v>564.7583684181604</v>
+        <v>564.758368402354</v>
       </c>
       <c r="D7" t="n">
-        <v>566.8633867548066</v>
+        <v>566.8637137561677</v>
       </c>
       <c r="E7" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="8">
@@ -939,16 +955,16 @@
         <v>22463</v>
       </c>
       <c r="B8" t="n">
-        <v>665.6884640360697</v>
+        <v>665.7709288501477</v>
       </c>
       <c r="C8" t="n">
-        <v>651.7583684181606</v>
+        <v>651.758368402354</v>
       </c>
       <c r="D8" t="n">
-        <v>654.2611707283057</v>
+        <v>654.2615118800909</v>
       </c>
       <c r="E8" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="9">
@@ -956,16 +972,16 @@
         <v>22494</v>
       </c>
       <c r="B9" t="n">
-        <v>657.70375401993</v>
+        <v>657.7981998242331</v>
       </c>
       <c r="C9" t="n">
-        <v>635.7583684181606</v>
+        <v>635.758368402354</v>
       </c>
       <c r="D9" t="n">
-        <v>638.5985276703576</v>
+        <v>638.5988778759347</v>
       </c>
       <c r="E9" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="10">
@@ -973,16 +989,16 @@
         <v>22525</v>
       </c>
       <c r="B10" t="n">
-        <v>552.139567958434</v>
+        <v>552.1766951281539</v>
       </c>
       <c r="C10" t="n">
-        <v>537.7583684181607</v>
+        <v>537.758368402354</v>
       </c>
       <c r="D10" t="n">
-        <v>540.8848160515855</v>
+        <v>540.8851714102969</v>
       </c>
       <c r="E10" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="11">
@@ -990,16 +1006,16 @@
         <v>22555</v>
       </c>
       <c r="B11" t="n">
-        <v>499.2813518240579</v>
+        <v>499.2889517522912</v>
       </c>
       <c r="C11" t="n">
-        <v>490.7583684181607</v>
+        <v>490.758368402354</v>
       </c>
       <c r="D11" t="n">
-        <v>494.1277213119118</v>
+        <v>494.1280789042856</v>
       </c>
       <c r="E11" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="12">
@@ -1007,16 +1023,16 @@
         <v>22586</v>
       </c>
       <c r="B12" t="n">
-        <v>432.1916548333424</v>
+        <v>432.1833504717112</v>
       </c>
       <c r="C12" t="n">
-        <v>419.7583684181607</v>
+        <v>419.758368402354</v>
       </c>
       <c r="D12" t="n">
-        <v>423.3338289973573</v>
+        <v>423.3341866681923</v>
       </c>
       <c r="E12" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
     <row r="13">
@@ -1024,16 +1040,16 @@
         <v>22616</v>
       </c>
       <c r="B13" t="n">
-        <v>476.9646782942283</v>
+        <v>476.9751711529959</v>
       </c>
       <c r="C13" t="n">
-        <v>461.7583684181607</v>
+        <v>461.758368402354</v>
       </c>
       <c r="D13" t="n">
-        <v>465.5087106661873</v>
+        <v>465.5090668626495</v>
       </c>
       <c r="E13" t="n">
-        <v>280.2986054229669</v>
+        <v>280.2986088298695</v>
       </c>
     </row>
   </sheetData>
@@ -1090,16 +1106,16 @@
         <v>404</v>
       </c>
       <c r="C2" t="n">
-        <v>437.9548692075684</v>
+        <v>437.9556101855629</v>
       </c>
       <c r="D2" t="n">
-        <v>439.6199789579319</v>
+        <v>439.6199788848658</v>
       </c>
       <c r="E2" t="n">
-        <v>441.4832559002728</v>
+        <v>441.4832544486218</v>
       </c>
       <c r="F2" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="3">
@@ -1110,16 +1126,16 @@
         <v>359</v>
       </c>
       <c r="C3" t="n">
-        <v>380.3201000007196</v>
+        <v>380.3159043781371</v>
       </c>
       <c r="D3" t="n">
-        <v>382.619978957932</v>
+        <v>382.6199788848658</v>
       </c>
       <c r="E3" t="n">
-        <v>385.3577697528492</v>
+        <v>385.3577676641654</v>
       </c>
       <c r="F3" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="4">
@@ -1130,16 +1146,16 @@
         <v>310</v>
       </c>
       <c r="C4" t="n">
-        <v>336.6917529799635</v>
+        <v>336.6847460941946</v>
       </c>
       <c r="D4" t="n">
-        <v>340.619978957932</v>
+        <v>340.6199788848658</v>
       </c>
       <c r="E4" t="n">
-        <v>342.8665445024415</v>
+        <v>342.8665424361785</v>
       </c>
       <c r="F4" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="5">
@@ -1150,16 +1166,16 @@
         <v>337</v>
       </c>
       <c r="C5" t="n">
-        <v>370.7020308870879</v>
+        <v>370.6951381151046</v>
       </c>
       <c r="D5" t="n">
-        <v>371.619978957932</v>
+        <v>371.6199788848658</v>
       </c>
       <c r="E5" t="n">
-        <v>374.1716604037737</v>
+        <v>374.1716583532292</v>
       </c>
       <c r="F5" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="6">
@@ -1170,16 +1186,16 @@
         <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>376.2295408132052</v>
+        <v>376.2198463250559</v>
       </c>
       <c r="D6" t="n">
-        <v>375.6199789579319</v>
+        <v>375.6199788848658</v>
       </c>
       <c r="E6" t="n">
-        <v>377.9847390870133</v>
+        <v>377.9847369853769</v>
       </c>
       <c r="F6" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="7">
@@ -1190,16 +1206,16 @@
         <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>353.673990727001</v>
+        <v>353.6628800102943</v>
       </c>
       <c r="D7" t="n">
-        <v>353.619978957932</v>
+        <v>353.6199788848658</v>
       </c>
       <c r="E7" t="n">
-        <v>356.0994603723406</v>
+        <v>356.0994583249864</v>
       </c>
       <c r="F7" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="8">
@@ -1210,16 +1226,16 @@
         <v>406</v>
       </c>
       <c r="C8" t="n">
-        <v>403.2653930793603</v>
+        <v>403.2511642898382</v>
       </c>
       <c r="D8" t="n">
-        <v>397.619978957932</v>
+        <v>397.6199788848658</v>
       </c>
       <c r="E8" t="n">
-        <v>400.0290682380028</v>
+        <v>400.029066143017</v>
       </c>
       <c r="F8" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="9">
@@ -1230,16 +1246,16 @@
         <v>396</v>
       </c>
       <c r="C9" t="n">
-        <v>389.866132963521</v>
+        <v>389.8504572864766</v>
       </c>
       <c r="D9" t="n">
-        <v>383.619978957932</v>
+        <v>383.6199788848658</v>
       </c>
       <c r="E9" t="n">
-        <v>386.0722617184022</v>
+        <v>386.0722596614081</v>
       </c>
       <c r="F9" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="10">
@@ -1250,16 +1266,16 @@
         <v>420</v>
       </c>
       <c r="C10" t="n">
-        <v>404.9958576916659</v>
+        <v>404.9812508317949</v>
       </c>
       <c r="D10" t="n">
-        <v>398.619978957932</v>
+        <v>398.6199788848658</v>
       </c>
       <c r="E10" t="n">
-        <v>401.0457577798234</v>
+        <v>401.0457556941369</v>
       </c>
       <c r="F10" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="11">
@@ -1270,16 +1286,16 @@
         <v>472</v>
       </c>
       <c r="C11" t="n">
-        <v>481.0672566023483</v>
+        <v>481.0575978707944</v>
       </c>
       <c r="D11" t="n">
-        <v>470.6199789579319</v>
+        <v>470.6199788848658</v>
       </c>
       <c r="E11" t="n">
-        <v>473.0620208628296</v>
+        <v>473.0620187980504</v>
       </c>
       <c r="F11" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="12">
@@ -1290,16 +1306,16 @@
         <v>548</v>
       </c>
       <c r="C12" t="n">
-        <v>537.6402432738989</v>
+        <v>537.6332321519039</v>
       </c>
       <c r="D12" t="n">
-        <v>526.6199789579319</v>
+        <v>526.6199788848658</v>
       </c>
       <c r="E12" t="n">
-        <v>529.0520416724441</v>
+        <v>529.0520395928104</v>
       </c>
       <c r="F12" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="13">
@@ -1310,16 +1326,16 @@
         <v>559</v>
       </c>
       <c r="C13" t="n">
-        <v>549.8971642185729</v>
+        <v>549.8954581630835</v>
       </c>
       <c r="D13" t="n">
-        <v>540.6199789579321</v>
+        <v>540.6199788848658</v>
       </c>
       <c r="E13" t="n">
-        <v>543.0581650035309</v>
+        <v>543.0581629342551</v>
       </c>
       <c r="F13" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="14">
@@ -1330,16 +1346,16 @@
         <v>463</v>
       </c>
       <c r="C14" t="n">
-        <v>478.643661104982</v>
+        <v>478.6396400852327</v>
       </c>
       <c r="D14" t="n">
-        <v>475.239957915864</v>
+        <v>475.2399577697315</v>
       </c>
       <c r="E14" t="n">
-        <v>479.5376635665748</v>
+        <v>479.5376600385297</v>
       </c>
       <c r="F14" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="15">
@@ -1350,16 +1366,16 @@
         <v>407</v>
       </c>
       <c r="C15" t="n">
-        <v>417.4644619191051</v>
+        <v>417.4538189944695</v>
       </c>
       <c r="D15" t="n">
-        <v>418.2399579158641</v>
+        <v>418.2399577697315</v>
       </c>
       <c r="E15" t="n">
-        <v>423.4144829588736</v>
+        <v>423.4144787986315</v>
       </c>
       <c r="F15" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="16">
@@ -1370,16 +1386,16 @@
         <v>362</v>
       </c>
       <c r="C16" t="n">
-        <v>371.5785966878221</v>
+        <v>371.5646600564982</v>
       </c>
       <c r="D16" t="n">
-        <v>376.2399579158641</v>
+        <v>376.2399577697315</v>
       </c>
       <c r="E16" t="n">
-        <v>380.9218430062214</v>
+        <v>380.9218388651456</v>
       </c>
       <c r="F16" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="17">
@@ -1390,16 +1406,16 @@
         <v>405</v>
       </c>
       <c r="C17" t="n">
-        <v>406.5330424638883</v>
+        <v>406.5182490715758</v>
       </c>
       <c r="D17" t="n">
-        <v>407.2399579158641</v>
+        <v>407.2399577697315</v>
       </c>
       <c r="E17" t="n">
-        <v>412.2278269830073</v>
+        <v>412.2278228598233</v>
       </c>
       <c r="F17" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="18">
@@ -1410,16 +1426,16 @@
         <v>417</v>
       </c>
       <c r="C18" t="n">
-        <v>412.2379400558975</v>
+        <v>412.2196225075866</v>
       </c>
       <c r="D18" t="n">
-        <v>411.239957915864</v>
+        <v>411.2399577697315</v>
       </c>
       <c r="E18" t="n">
-        <v>416.0403730064619</v>
+        <v>416.0403688307443</v>
       </c>
       <c r="F18" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="19">
@@ -1430,16 +1446,16 @@
         <v>391</v>
       </c>
       <c r="C19" t="n">
-        <v>387.2142303592401</v>
+        <v>387.193551308148</v>
       </c>
       <c r="D19" t="n">
-        <v>389.2399579158641</v>
+        <v>389.2399577697315</v>
       </c>
       <c r="E19" t="n">
-        <v>394.1554211371635</v>
+        <v>394.1554170166791</v>
       </c>
       <c r="F19" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="20">
@@ -1450,16 +1466,16 @@
         <v>419</v>
       </c>
       <c r="C20" t="n">
-        <v>438.4799051524628</v>
+        <v>438.4548410913514</v>
       </c>
       <c r="D20" t="n">
-        <v>433.2399579158641</v>
+        <v>433.2399577697315</v>
       </c>
       <c r="E20" t="n">
-        <v>438.0848284472332</v>
+        <v>438.0848242784931</v>
       </c>
       <c r="F20" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="21">
@@ -1470,16 +1486,16 @@
         <v>461</v>
       </c>
       <c r="C21" t="n">
-        <v>424.054132065201</v>
+        <v>424.0266732669652</v>
       </c>
       <c r="D21" t="n">
-        <v>419.2399579158641</v>
+        <v>419.2399577697315</v>
       </c>
       <c r="E21" t="n">
-        <v>424.128144990551</v>
+        <v>424.1281408602106</v>
       </c>
       <c r="F21" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="22">
@@ -1490,16 +1506,16 @@
         <v>472</v>
       </c>
       <c r="C22" t="n">
-        <v>441.2269803491424</v>
+        <v>441.2007851274286</v>
       </c>
       <c r="D22" t="n">
-        <v>434.2399579158641</v>
+        <v>434.2399577697315</v>
       </c>
       <c r="E22" t="n">
-        <v>439.101565539334</v>
+        <v>439.1015613800356</v>
       </c>
       <c r="F22" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="23">
@@ -1510,16 +1526,16 @@
         <v>535</v>
       </c>
       <c r="C23" t="n">
-        <v>521.5738705303223</v>
+        <v>521.555054502196</v>
       </c>
       <c r="D23" t="n">
-        <v>506.239957915864</v>
+        <v>506.2399577697315</v>
       </c>
       <c r="E23" t="n">
-        <v>511.1178749576507</v>
+        <v>511.1178708194319</v>
       </c>
       <c r="F23" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="24">
@@ -1530,16 +1546,16 @@
         <v>622</v>
       </c>
       <c r="C24" t="n">
-        <v>581.7105092230923</v>
+        <v>581.6949392233171</v>
       </c>
       <c r="D24" t="n">
-        <v>562.239957915864</v>
+        <v>562.2399577697315</v>
       </c>
       <c r="E24" t="n">
-        <v>567.1078673354551</v>
+        <v>567.1078631822702</v>
       </c>
       <c r="F24" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="25">
@@ -1550,16 +1566,16 @@
         <v>606</v>
       </c>
       <c r="C25" t="n">
-        <v>595.5211072662592</v>
+        <v>595.5136710114843</v>
       </c>
       <c r="D25" t="n">
-        <v>576.2399579158641</v>
+        <v>576.2399577697315</v>
       </c>
       <c r="E25" t="n">
-        <v>581.1140081125851</v>
+        <v>581.11400396983</v>
       </c>
       <c r="F25" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="26">
@@ -1570,16 +1586,16 @@
         <v>508</v>
       </c>
       <c r="C26" t="n">
-        <v>520.1061664033766</v>
+        <v>520.0953617181948</v>
       </c>
       <c r="D26" t="n">
-        <v>510.8599368737961</v>
+        <v>510.8599366545973</v>
       </c>
       <c r="E26" t="n">
-        <v>517.5934959705625</v>
+        <v>517.5934903689916</v>
       </c>
       <c r="F26" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="27">
@@ -1590,16 +1606,16 @@
         <v>461</v>
       </c>
       <c r="C27" t="n">
-        <v>456.0837955806485</v>
+        <v>456.0644298538978</v>
       </c>
       <c r="D27" t="n">
-        <v>453.8599368737961</v>
+        <v>453.8599366545973</v>
       </c>
       <c r="E27" t="n">
-        <v>461.4703219315973</v>
+        <v>461.4703156978592</v>
       </c>
       <c r="F27" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="28">
@@ -1610,16 +1626,16 @@
         <v>390</v>
       </c>
       <c r="C28" t="n">
-        <v>408.0950667597602</v>
+        <v>408.0718813249924</v>
       </c>
       <c r="D28" t="n">
-        <v>411.8599368737961</v>
+        <v>411.8599366545973</v>
       </c>
       <c r="E28" t="n">
-        <v>418.9776779483029</v>
+        <v>418.977671733712</v>
       </c>
       <c r="F28" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
     <row r="29">
@@ -1630,16 +1646,16 @@
         <v>432</v>
       </c>
       <c r="C29" t="n">
-        <v>444.4880377917441</v>
+        <v>444.4628048072218</v>
       </c>
       <c r="D29" t="n">
-        <v>442.8599368737961</v>
+        <v>442.8599366545973</v>
       </c>
       <c r="E29" t="n">
-        <v>450.2836643983312</v>
+        <v>450.2836582016444</v>
       </c>
       <c r="F29" t="n">
-        <v>242.2327224395236</v>
+        <v>242.2327214287559</v>
       </c>
     </row>
   </sheetData>
